--- a/SFN/copesXage.xlsx
+++ b/SFN/copesXage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avidachs/Documents/GitHub/rf1-sra-trust/SFN/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3532AFF-77F3-A341-8B34-BD8EAC890D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD07B288-8512-F140-AA87-E9EFD54F6645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{237D927A-4980-744D-8F94-C4A707B37354}"/>
   </bookViews>

--- a/SFN/copesXage.xlsx
+++ b/SFN/copesXage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avidachs/Documents/GitHub/rf1-sra-trust/SFN/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB4C4A0-4061-8D45-9132-2392D7BF0438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B7D209-661C-1F47-9699-4E8D2C859FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="17780" windowHeight="16120" xr2:uid="{237D927A-4980-744D-8F94-C4A707B37354}"/>
   </bookViews>
